--- a/Scrape PHEI/2026-04-April/Yield-Curve-02-April-2026.xlsx
+++ b/Scrape PHEI/2026-04-April/Yield-Curve-02-April-2026.xlsx
@@ -750,7 +750,7 @@
         <v>0.069031</v>
       </c>
       <c r="C29" t="n">
-        <v>0.06984715793287055</v>
+        <v>0.06984715793287033</v>
       </c>
     </row>
     <row r="30">
